--- a/templates/1.7. Roller _ Template_2026_05_01_BiT.xlsx
+++ b/templates/1.7. Roller _ Template_2026_05_01_BiT.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CONSULTANCY\CMI\analytics-2026\Analysis-Templates\NPN_Water_Template_2026__01_BiT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\CMI-NPN\CMI-DATABASE\Templates-BiT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F54FA94-FC94-480E-9742-AEB791778137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF622013-2732-450B-9231-EAF5A0C59E16}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="1380" windowWidth="20490" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roller" sheetId="25" r:id="rId1"/>
-    <sheet name="MPDM 1" sheetId="11" r:id="rId2"/>
+    <sheet name="MPDM" sheetId="11" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'MPDM 1'!$A$1:$T$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">MPDM!$A$1:$T$120</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Roller!$A$1:$P$112</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -564,10 +571,12 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -931,6 +940,15 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="3" fillId="7" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="7" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -961,6 +979,15 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -972,24 +999,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="7" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="7" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1423,64 +1432,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
     </row>
     <row r="2" spans="2:16" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
     </row>
     <row r="5" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -1488,10 +1497,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="37"/>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="46"/>
+      <c r="F6" s="49"/>
       <c r="G6" s="37"/>
       <c r="K6" s="38" t="s">
         <v>0</v>
@@ -1506,49 +1515,49 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="39" t="s">
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="L9" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="M9" s="39" t="s">
+      <c r="M9" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="39" t="s">
+      <c r="N9" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="O9" s="39" t="s">
+      <c r="O9" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="P9" s="39" t="s">
+      <c r="P9" s="42" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
       <c r="F10" s="4" t="s">
         <v>58</v>
       </c>
@@ -1564,12 +1573,12 @@
       <c r="J10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
     </row>
     <row r="11" spans="2:16" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
@@ -1589,19 +1598,19 @@
         <v>#DIV/0!</v>
       </c>
       <c r="M11" s="34" t="e">
-        <f>'MPDM 1'!H118*F11*H11*I11</f>
+        <f>MPDM!H118*F11*H11*I11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N11" s="34" t="e">
-        <f>'MPDM 1'!K118*F11*H11*I11</f>
+        <f>MPDM!K118*F11*H11*I11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O11" s="35" t="e">
-        <f>'MPDM 1'!H119</f>
+        <f>MPDM!H119</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P11" s="35" t="e">
-        <f>'MPDM 1'!K119</f>
+        <f>MPDM!K119</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2921,7 +2930,7 @@
       <c r="J83" s="6"/>
       <c r="K83" s="6"/>
       <c r="L83" s="5" t="e">
-        <f t="shared" ref="L83:L102" si="2">(F83*G83*H83*I83)/J83</f>
+        <f t="shared" ref="L83:L101" si="2">(F83*G83*H83*I83)/J83</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3412,12 +3421,12 @@
       </c>
     </row>
     <row r="111" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B111" s="56" t="s">
+      <c r="B111" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C111" s="56"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="56"/>
+      <c r="C111" s="41"/>
+      <c r="D111" s="41"/>
+      <c r="E111" s="41"/>
       <c r="F111" s="1" t="e">
         <f>AVERAGE(F11:F110)</f>
         <v>#DIV/0!</v>
@@ -3445,6 +3454,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="O9:O10"/>
     <mergeCell ref="B111:E111"/>
     <mergeCell ref="P9:P10"/>
     <mergeCell ref="B1:L1"/>
@@ -3461,7 +3471,6 @@
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="N9:N10"/>
-    <mergeCell ref="O9:O10"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3502,75 +3511,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
       <c r="N1" s="8"/>
     </row>
     <row r="2" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
       <c r="N2" s="8"/>
     </row>
     <row r="3" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
       <c r="N4" s="9"/>
     </row>
     <row r="5" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -3578,8 +3587,8 @@
       <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="56"/>
       <c r="F6" s="14" t="s">
         <v>0</v>
       </c>
@@ -3592,8 +3601,8 @@
       <c r="A8" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="56"/>
       <c r="F8" s="14" t="s">
         <v>12</v>
       </c>
@@ -3605,53 +3614,53 @@
       <c r="A9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="50"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="56"/>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
     </row>
     <row r="11" spans="1:27" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="54"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
       <c r="M11" s="16"/>
-      <c r="O11" s="53" t="s">
+      <c r="O11" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="55"/>
-      <c r="V11" s="53" t="s">
+      <c r="P11" s="53"/>
+      <c r="Q11" s="53"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="53"/>
+      <c r="T11" s="54"/>
+      <c r="V11" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="W11" s="54"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="54"/>
-      <c r="Z11" s="54"/>
-      <c r="AA11" s="55"/>
+      <c r="W11" s="53"/>
+      <c r="X11" s="53"/>
+      <c r="Y11" s="53"/>
+      <c r="Z11" s="53"/>
+      <c r="AA11" s="54"/>
     </row>
     <row r="12" spans="1:27" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
+      <c r="A12" s="58"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="4" t="s">
         <v>17</v>
       </c>
@@ -3727,27 +3736,27 @@
         <v>1</v>
       </c>
       <c r="B13" s="18"/>
-      <c r="C13" s="57">
+      <c r="C13" s="39">
         <f>IF(SUM($V13:$AA13), ROUND(V13/SUM($V13:$AA13), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="57">
+      <c r="D13" s="39">
         <f t="shared" ref="D13:H28" si="0">IF(SUM($V13:$AA13), ROUND(W13/SUM($V13:$AA13), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="57">
+      <c r="E13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13" s="57">
+      <c r="F13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="57">
+      <c r="G13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3807,27 +3816,27 @@
         <v>2</v>
       </c>
       <c r="B14" s="21"/>
-      <c r="C14" s="57">
+      <c r="C14" s="39">
         <f t="shared" ref="C14:H68" si="2">IF(SUM($V14:$AA14), ROUND(V14/SUM($V14:$AA14), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="57">
+      <c r="G14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="57">
+      <c r="H14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3887,27 +3896,27 @@
         <v>3</v>
       </c>
       <c r="B15" s="21"/>
-      <c r="C15" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D15" s="57">
+      <c r="C15" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G15" s="57">
+      <c r="G15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="57">
+      <c r="H15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3967,27 +3976,27 @@
         <v>4</v>
       </c>
       <c r="B16" s="21"/>
-      <c r="C16" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D16" s="57">
+      <c r="C16" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="57">
+      <c r="E16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="57">
+      <c r="F16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="57">
+      <c r="G16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4047,27 +4056,27 @@
         <v>5</v>
       </c>
       <c r="B17" s="21"/>
-      <c r="C17" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D17" s="57">
+      <c r="C17" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="57">
+      <c r="F17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="57">
+      <c r="G17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="57">
+      <c r="H17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4127,27 +4136,27 @@
         <v>6</v>
       </c>
       <c r="B18" s="21"/>
-      <c r="C18" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D18" s="57">
+      <c r="C18" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="57">
+      <c r="E18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="57">
+      <c r="F18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="57">
+      <c r="G18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="57">
+      <c r="H18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4207,27 +4216,27 @@
         <v>7</v>
       </c>
       <c r="B19" s="21"/>
-      <c r="C19" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D19" s="57">
+      <c r="C19" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E19" s="57">
+      <c r="E19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F19" s="57">
+      <c r="F19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="57">
+      <c r="G19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H19" s="57">
+      <c r="H19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4287,27 +4296,27 @@
         <v>8</v>
       </c>
       <c r="B20" s="21"/>
-      <c r="C20" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D20" s="57">
+      <c r="C20" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="57">
+      <c r="F20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G20" s="57">
+      <c r="G20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="57">
+      <c r="H20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4367,27 +4376,27 @@
         <v>9</v>
       </c>
       <c r="B21" s="21"/>
-      <c r="C21" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D21" s="57">
+      <c r="C21" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="57">
+      <c r="F21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="57">
+      <c r="G21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="57">
+      <c r="H21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4447,27 +4456,27 @@
         <v>10</v>
       </c>
       <c r="B22" s="21"/>
-      <c r="C22" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D22" s="57">
+      <c r="C22" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="57">
+      <c r="F22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="57">
+      <c r="G22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H22" s="57">
+      <c r="H22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4527,27 +4536,27 @@
         <v>11</v>
       </c>
       <c r="B23" s="21"/>
-      <c r="C23" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D23" s="57">
+      <c r="C23" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D23" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E23" s="57">
+      <c r="E23" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="57">
+      <c r="F23" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G23" s="57">
+      <c r="G23" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H23" s="57">
+      <c r="H23" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4607,27 +4616,27 @@
         <v>12</v>
       </c>
       <c r="B24" s="21"/>
-      <c r="C24" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D24" s="57">
+      <c r="C24" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E24" s="57">
+      <c r="E24" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F24" s="57">
+      <c r="F24" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G24" s="57">
+      <c r="G24" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4687,27 +4696,27 @@
         <v>13</v>
       </c>
       <c r="B25" s="21"/>
-      <c r="C25" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D25" s="57">
+      <c r="C25" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="57">
+      <c r="E25" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="57">
+      <c r="F25" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G25" s="57">
+      <c r="G25" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H25" s="57">
+      <c r="H25" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4767,27 +4776,27 @@
         <v>14</v>
       </c>
       <c r="B26" s="21"/>
-      <c r="C26" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D26" s="57">
+      <c r="C26" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="57">
+      <c r="E26" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="57">
+      <c r="F26" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="57">
+      <c r="G26" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4847,27 +4856,27 @@
         <v>15</v>
       </c>
       <c r="B27" s="21"/>
-      <c r="C27" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D27" s="57">
+      <c r="C27" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E27" s="57">
+      <c r="E27" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F27" s="57">
+      <c r="F27" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G27" s="57">
+      <c r="G27" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H27" s="57">
+      <c r="H27" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4927,27 +4936,27 @@
         <v>16</v>
       </c>
       <c r="B28" s="21"/>
-      <c r="C28" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D28" s="57">
+      <c r="C28" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="57">
+      <c r="E28" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F28" s="57">
+      <c r="F28" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G28" s="57">
+      <c r="G28" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H28" s="57">
+      <c r="H28" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5007,27 +5016,27 @@
         <v>17</v>
       </c>
       <c r="B29" s="21"/>
-      <c r="C29" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D29" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="57">
+      <c r="C29" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5087,27 +5096,27 @@
         <v>18</v>
       </c>
       <c r="B30" s="21"/>
-      <c r="C30" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D30" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="57">
+      <c r="C30" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5167,27 +5176,27 @@
         <v>19</v>
       </c>
       <c r="B31" s="21"/>
-      <c r="C31" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D31" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="57">
+      <c r="C31" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5247,27 +5256,27 @@
         <v>20</v>
       </c>
       <c r="B32" s="21"/>
-      <c r="C32" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D32" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E32" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="57">
+      <c r="C32" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E32" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5327,27 +5336,27 @@
         <v>21</v>
       </c>
       <c r="B33" s="21"/>
-      <c r="C33" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D33" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="57">
+      <c r="C33" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E33" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5407,27 +5416,27 @@
         <v>22</v>
       </c>
       <c r="B34" s="21"/>
-      <c r="C34" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D34" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E34" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="57">
+      <c r="C34" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E34" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5487,27 +5496,27 @@
         <v>23</v>
       </c>
       <c r="B35" s="21"/>
-      <c r="C35" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D35" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E35" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="57">
+      <c r="C35" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E35" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5567,27 +5576,27 @@
         <v>24</v>
       </c>
       <c r="B36" s="21"/>
-      <c r="C36" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D36" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E36" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="57">
+      <c r="C36" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E36" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5647,27 +5656,27 @@
         <v>25</v>
       </c>
       <c r="B37" s="21"/>
-      <c r="C37" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D37" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E37" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G37" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="57">
+      <c r="C37" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E37" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5727,27 +5736,27 @@
         <v>26</v>
       </c>
       <c r="B38" s="21"/>
-      <c r="C38" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D38" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E38" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="57">
+      <c r="C38" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E38" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5807,27 +5816,27 @@
         <v>27</v>
       </c>
       <c r="B39" s="21"/>
-      <c r="C39" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D39" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E39" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="57">
+      <c r="C39" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E39" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5887,27 +5896,27 @@
         <v>28</v>
       </c>
       <c r="B40" s="21"/>
-      <c r="C40" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D40" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E40" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="57">
+      <c r="C40" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E40" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5967,27 +5976,27 @@
         <v>29</v>
       </c>
       <c r="B41" s="21"/>
-      <c r="C41" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D41" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E41" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G41" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="57">
+      <c r="C41" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E41" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6047,27 +6056,27 @@
         <v>30</v>
       </c>
       <c r="B42" s="21"/>
-      <c r="C42" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D42" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E42" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="57">
+      <c r="C42" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E42" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G42" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6127,27 +6136,27 @@
         <v>31</v>
       </c>
       <c r="B43" s="21"/>
-      <c r="C43" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D43" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E43" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="57">
+      <c r="C43" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E43" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G43" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6207,27 +6216,27 @@
         <v>32</v>
       </c>
       <c r="B44" s="21"/>
-      <c r="C44" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D44" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E44" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F44" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G44" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="57">
+      <c r="C44" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E44" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6287,27 +6296,27 @@
         <v>33</v>
       </c>
       <c r="B45" s="21"/>
-      <c r="C45" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D45" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E45" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G45" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="57">
+      <c r="C45" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E45" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G45" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6367,27 +6376,27 @@
         <v>34</v>
       </c>
       <c r="B46" s="21"/>
-      <c r="C46" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D46" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E46" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G46" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="57">
+      <c r="C46" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D46" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E46" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G46" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6447,27 +6456,27 @@
         <v>35</v>
       </c>
       <c r="B47" s="21"/>
-      <c r="C47" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D47" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E47" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H47" s="57">
+      <c r="C47" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D47" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E47" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6527,27 +6536,27 @@
         <v>36</v>
       </c>
       <c r="B48" s="21"/>
-      <c r="C48" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D48" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E48" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="57">
+      <c r="C48" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D48" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E48" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6607,27 +6616,27 @@
         <v>37</v>
       </c>
       <c r="B49" s="21"/>
-      <c r="C49" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D49" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E49" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="57">
+      <c r="C49" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D49" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E49" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6687,27 +6696,27 @@
         <v>38</v>
       </c>
       <c r="B50" s="21"/>
-      <c r="C50" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D50" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E50" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G50" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="57">
+      <c r="C50" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D50" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E50" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6767,27 +6776,27 @@
         <v>39</v>
       </c>
       <c r="B51" s="21"/>
-      <c r="C51" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D51" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E51" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="57">
+      <c r="C51" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D51" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E51" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6847,27 +6856,27 @@
         <v>40</v>
       </c>
       <c r="B52" s="21"/>
-      <c r="C52" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D52" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E52" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="57">
+      <c r="C52" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D52" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E52" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6927,27 +6936,27 @@
         <v>41</v>
       </c>
       <c r="B53" s="21"/>
-      <c r="C53" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D53" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E53" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F53" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G53" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H53" s="57">
+      <c r="C53" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D53" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E53" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7007,27 +7016,27 @@
         <v>42</v>
       </c>
       <c r="B54" s="21"/>
-      <c r="C54" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D54" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E54" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F54" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G54" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="57">
+      <c r="C54" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D54" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E54" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H54" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7087,27 +7096,27 @@
         <v>43</v>
       </c>
       <c r="B55" s="21"/>
-      <c r="C55" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D55" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E55" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="57">
+      <c r="C55" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D55" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E55" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G55" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7167,27 +7176,27 @@
         <v>44</v>
       </c>
       <c r="B56" s="21"/>
-      <c r="C56" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D56" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E56" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F56" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G56" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="57">
+      <c r="C56" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D56" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E56" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G56" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7247,27 +7256,27 @@
         <v>45</v>
       </c>
       <c r="B57" s="21"/>
-      <c r="C57" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D57" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E57" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G57" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H57" s="57">
+      <c r="C57" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D57" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E57" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G57" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H57" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7327,27 +7336,27 @@
         <v>46</v>
       </c>
       <c r="B58" s="21"/>
-      <c r="C58" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D58" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E58" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G58" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="57">
+      <c r="C58" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D58" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E58" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G58" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7407,27 +7416,27 @@
         <v>47</v>
       </c>
       <c r="B59" s="21"/>
-      <c r="C59" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D59" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E59" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F59" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G59" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H59" s="57">
+      <c r="C59" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D59" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E59" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F59" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G59" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H59" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7487,27 +7496,27 @@
         <v>48</v>
       </c>
       <c r="B60" s="21"/>
-      <c r="C60" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D60" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E60" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F60" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G60" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H60" s="57">
+      <c r="C60" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D60" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E60" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F60" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G60" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H60" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7567,27 +7576,27 @@
         <v>49</v>
       </c>
       <c r="B61" s="21"/>
-      <c r="C61" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D61" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E61" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F61" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G61" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H61" s="57">
+      <c r="C61" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D61" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E61" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G61" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H61" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7647,27 +7656,27 @@
         <v>50</v>
       </c>
       <c r="B62" s="21"/>
-      <c r="C62" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D62" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E62" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G62" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="57">
+      <c r="C62" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D62" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E62" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H62" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7727,27 +7736,27 @@
         <v>51</v>
       </c>
       <c r="B63" s="21"/>
-      <c r="C63" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D63" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E63" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F63" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G63" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H63" s="57">
+      <c r="C63" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D63" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E63" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G63" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H63" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7807,27 +7816,27 @@
         <v>52</v>
       </c>
       <c r="B64" s="21"/>
-      <c r="C64" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D64" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E64" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F64" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G64" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="57">
+      <c r="C64" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D64" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E64" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7887,27 +7896,27 @@
         <v>53</v>
       </c>
       <c r="B65" s="21"/>
-      <c r="C65" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D65" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E65" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F65" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G65" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="57">
+      <c r="C65" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D65" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E65" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H65" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7967,27 +7976,27 @@
         <v>54</v>
       </c>
       <c r="B66" s="21"/>
-      <c r="C66" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D66" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E66" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F66" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G66" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="57">
+      <c r="C66" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D66" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E66" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F66" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G66" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H66" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8047,27 +8056,27 @@
         <v>55</v>
       </c>
       <c r="B67" s="21"/>
-      <c r="C67" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D67" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E67" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F67" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G67" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H67" s="57">
+      <c r="C67" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D67" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E67" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F67" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G67" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H67" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8127,27 +8136,27 @@
         <v>56</v>
       </c>
       <c r="B68" s="21"/>
-      <c r="C68" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D68" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E68" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F68" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G68" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H68" s="57">
+      <c r="C68" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D68" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E68" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G68" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H68" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8207,27 +8216,27 @@
         <v>57</v>
       </c>
       <c r="B69" s="21"/>
-      <c r="C69" s="57">
+      <c r="C69" s="39">
         <f t="shared" ref="C69:H111" si="9">IF(SUM($V69:$AA69), ROUND(V69/SUM($V69:$AA69), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E69" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F69" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G69" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H69" s="57">
+      <c r="D69" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E69" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G69" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8287,27 +8296,27 @@
         <v>58</v>
       </c>
       <c r="B70" s="21"/>
-      <c r="C70" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D70" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E70" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F70" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G70" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H70" s="57">
+      <c r="C70" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D70" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E70" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G70" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8367,27 +8376,27 @@
         <v>59</v>
       </c>
       <c r="B71" s="21"/>
-      <c r="C71" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D71" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E71" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F71" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G71" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H71" s="57">
+      <c r="C71" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D71" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E71" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F71" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G71" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8447,27 +8456,27 @@
         <v>60</v>
       </c>
       <c r="B72" s="21"/>
-      <c r="C72" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D72" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E72" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F72" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G72" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H72" s="57">
+      <c r="C72" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D72" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E72" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F72" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G72" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H72" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8527,27 +8536,27 @@
         <v>61</v>
       </c>
       <c r="B73" s="21"/>
-      <c r="C73" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D73" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E73" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F73" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G73" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="57">
+      <c r="C73" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D73" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E73" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G73" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8607,27 +8616,27 @@
         <v>62</v>
       </c>
       <c r="B74" s="21"/>
-      <c r="C74" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D74" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E74" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F74" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G74" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="57">
+      <c r="C74" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D74" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E74" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8687,27 +8696,27 @@
         <v>63</v>
       </c>
       <c r="B75" s="21"/>
-      <c r="C75" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D75" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E75" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F75" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G75" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="57">
+      <c r="C75" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D75" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E75" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G75" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H75" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8767,27 +8776,27 @@
         <v>64</v>
       </c>
       <c r="B76" s="21"/>
-      <c r="C76" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D76" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E76" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G76" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="57">
+      <c r="C76" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D76" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E76" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G76" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H76" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8847,27 +8856,27 @@
         <v>65</v>
       </c>
       <c r="B77" s="21"/>
-      <c r="C77" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D77" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E77" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F77" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G77" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H77" s="57">
+      <c r="C77" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D77" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E77" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F77" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G77" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H77" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8927,27 +8936,27 @@
         <v>66</v>
       </c>
       <c r="B78" s="21"/>
-      <c r="C78" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D78" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E78" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F78" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G78" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H78" s="57">
+      <c r="C78" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D78" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E78" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F78" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G78" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H78" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9007,27 +9016,27 @@
         <v>67</v>
       </c>
       <c r="B79" s="21"/>
-      <c r="C79" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D79" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E79" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G79" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="57">
+      <c r="C79" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D79" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E79" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F79" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G79" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H79" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9087,27 +9096,27 @@
         <v>68</v>
       </c>
       <c r="B80" s="21"/>
-      <c r="C80" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D80" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E80" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F80" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G80" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H80" s="57">
+      <c r="C80" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D80" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E80" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G80" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H80" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9167,27 +9176,27 @@
         <v>69</v>
       </c>
       <c r="B81" s="21"/>
-      <c r="C81" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D81" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E81" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F81" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G81" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H81" s="57">
+      <c r="C81" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D81" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E81" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G81" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H81" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9247,27 +9256,27 @@
         <v>70</v>
       </c>
       <c r="B82" s="21"/>
-      <c r="C82" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D82" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E82" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F82" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G82" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H82" s="57">
+      <c r="C82" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D82" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E82" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G82" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H82" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9327,27 +9336,27 @@
         <v>71</v>
       </c>
       <c r="B83" s="21"/>
-      <c r="C83" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D83" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E83" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F83" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G83" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H83" s="57">
+      <c r="C83" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D83" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E83" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G83" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H83" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9407,27 +9416,27 @@
         <v>72</v>
       </c>
       <c r="B84" s="21"/>
-      <c r="C84" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D84" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E84" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F84" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G84" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H84" s="57">
+      <c r="C84" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D84" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E84" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G84" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H84" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9487,27 +9496,27 @@
         <v>73</v>
       </c>
       <c r="B85" s="21"/>
-      <c r="C85" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D85" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E85" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G85" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="57">
+      <c r="C85" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D85" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E85" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9567,27 +9576,27 @@
         <v>74</v>
       </c>
       <c r="B86" s="21"/>
-      <c r="C86" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D86" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E86" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F86" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G86" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H86" s="57">
+      <c r="C86" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D86" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E86" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F86" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G86" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H86" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9647,27 +9656,27 @@
         <v>75</v>
       </c>
       <c r="B87" s="21"/>
-      <c r="C87" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D87" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E87" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F87" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G87" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H87" s="57">
+      <c r="C87" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D87" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E87" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F87" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G87" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H87" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9727,27 +9736,27 @@
         <v>76</v>
       </c>
       <c r="B88" s="21"/>
-      <c r="C88" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D88" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E88" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F88" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G88" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H88" s="57">
+      <c r="C88" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D88" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E88" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G88" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H88" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9807,27 +9816,27 @@
         <v>77</v>
       </c>
       <c r="B89" s="21"/>
-      <c r="C89" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D89" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E89" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F89" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G89" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H89" s="57">
+      <c r="C89" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D89" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E89" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F89" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G89" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H89" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9887,27 +9896,27 @@
         <v>78</v>
       </c>
       <c r="B90" s="21"/>
-      <c r="C90" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D90" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E90" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F90" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G90" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H90" s="57">
+      <c r="C90" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D90" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E90" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F90" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G90" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H90" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9967,27 +9976,27 @@
         <v>79</v>
       </c>
       <c r="B91" s="21"/>
-      <c r="C91" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D91" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E91" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F91" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G91" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H91" s="57">
+      <c r="C91" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D91" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E91" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F91" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G91" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H91" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10047,27 +10056,27 @@
         <v>80</v>
       </c>
       <c r="B92" s="21"/>
-      <c r="C92" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D92" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E92" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F92" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G92" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H92" s="57">
+      <c r="C92" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D92" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E92" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F92" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G92" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H92" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10127,27 +10136,27 @@
         <v>81</v>
       </c>
       <c r="B93" s="21"/>
-      <c r="C93" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D93" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E93" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F93" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G93" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H93" s="57">
+      <c r="C93" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D93" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E93" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F93" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G93" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H93" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10207,27 +10216,27 @@
         <v>82</v>
       </c>
       <c r="B94" s="21"/>
-      <c r="C94" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D94" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E94" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F94" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G94" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H94" s="57">
+      <c r="C94" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D94" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E94" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G94" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H94" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10287,27 +10296,27 @@
         <v>83</v>
       </c>
       <c r="B95" s="21"/>
-      <c r="C95" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D95" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E95" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F95" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G95" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H95" s="57">
+      <c r="C95" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D95" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E95" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G95" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H95" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10367,27 +10376,27 @@
         <v>84</v>
       </c>
       <c r="B96" s="21"/>
-      <c r="C96" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D96" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E96" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F96" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G96" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H96" s="57">
+      <c r="C96" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D96" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E96" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F96" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G96" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H96" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10447,27 +10456,27 @@
         <v>85</v>
       </c>
       <c r="B97" s="21"/>
-      <c r="C97" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D97" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E97" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F97" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G97" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H97" s="57">
+      <c r="C97" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D97" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E97" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F97" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G97" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H97" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10527,27 +10536,27 @@
         <v>86</v>
       </c>
       <c r="B98" s="21"/>
-      <c r="C98" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D98" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E98" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F98" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G98" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H98" s="57">
+      <c r="C98" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D98" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E98" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F98" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G98" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10607,27 +10616,27 @@
         <v>87</v>
       </c>
       <c r="B99" s="21"/>
-      <c r="C99" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D99" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E99" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F99" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G99" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H99" s="57">
+      <c r="C99" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D99" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E99" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F99" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G99" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H99" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10687,27 +10696,27 @@
         <v>88</v>
       </c>
       <c r="B100" s="21"/>
-      <c r="C100" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D100" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E100" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F100" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G100" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H100" s="57">
+      <c r="C100" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D100" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E100" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F100" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G100" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H100" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10767,27 +10776,27 @@
         <v>89</v>
       </c>
       <c r="B101" s="21"/>
-      <c r="C101" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D101" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E101" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F101" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G101" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H101" s="57">
+      <c r="C101" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D101" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E101" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F101" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G101" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H101" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10847,27 +10856,27 @@
         <v>90</v>
       </c>
       <c r="B102" s="21"/>
-      <c r="C102" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D102" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E102" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F102" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G102" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H102" s="57">
+      <c r="C102" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D102" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E102" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F102" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G102" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H102" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10927,27 +10936,27 @@
         <v>91</v>
       </c>
       <c r="B103" s="21"/>
-      <c r="C103" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D103" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E103" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G103" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H103" s="57">
+      <c r="C103" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D103" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E103" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G103" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H103" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11007,27 +11016,27 @@
         <v>92</v>
       </c>
       <c r="B104" s="21"/>
-      <c r="C104" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D104" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E104" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F104" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G104" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H104" s="57">
+      <c r="C104" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D104" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E104" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F104" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G104" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H104" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11087,27 +11096,27 @@
         <v>93</v>
       </c>
       <c r="B105" s="21"/>
-      <c r="C105" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D105" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E105" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F105" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G105" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H105" s="57">
+      <c r="C105" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D105" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E105" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G105" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H105" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11167,27 +11176,27 @@
         <v>94</v>
       </c>
       <c r="B106" s="21"/>
-      <c r="C106" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D106" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E106" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F106" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G106" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H106" s="57">
+      <c r="C106" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D106" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E106" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F106" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G106" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H106" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11247,27 +11256,27 @@
         <v>95</v>
       </c>
       <c r="B107" s="21"/>
-      <c r="C107" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D107" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E107" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F107" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G107" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H107" s="57">
+      <c r="C107" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D107" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E107" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F107" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G107" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H107" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11327,27 +11336,27 @@
         <v>96</v>
       </c>
       <c r="B108" s="21"/>
-      <c r="C108" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D108" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E108" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F108" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G108" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H108" s="57">
+      <c r="C108" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D108" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E108" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F108" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G108" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H108" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11407,27 +11416,27 @@
         <v>97</v>
       </c>
       <c r="B109" s="21"/>
-      <c r="C109" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D109" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E109" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F109" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G109" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H109" s="57">
+      <c r="C109" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D109" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E109" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F109" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G109" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H109" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11487,27 +11496,27 @@
         <v>98</v>
       </c>
       <c r="B110" s="21"/>
-      <c r="C110" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D110" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E110" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F110" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G110" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H110" s="57">
+      <c r="C110" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D110" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E110" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F110" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G110" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H110" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11567,27 +11576,27 @@
         <v>99</v>
       </c>
       <c r="B111" s="21"/>
-      <c r="C111" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D111" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E111" s="57">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F111" s="57">
+      <c r="C111" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D111" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E111" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F111" s="39">
         <f t="shared" ref="F111:H112" si="17">IF(SUM($V111:$AA111), ROUND(Y111/SUM($V111:$AA111), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="G111" s="57">
+      <c r="G111" s="39">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H111" s="57">
+      <c r="H111" s="39">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
@@ -11647,27 +11656,27 @@
         <v>100</v>
       </c>
       <c r="B112" s="23"/>
-      <c r="C112" s="58">
+      <c r="C112" s="40">
         <f t="shared" ref="C112:E112" si="18">IF(SUM($V112:$AA112), ROUND(V112/SUM($V112:$AA112), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="D112" s="58">
+      <c r="D112" s="40">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="E112" s="58">
+      <c r="E112" s="40">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="F112" s="58">
+      <c r="F112" s="40">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G112" s="58">
+      <c r="G112" s="40">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H112" s="58">
+      <c r="H112" s="40">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
@@ -11728,7 +11737,7 @@
         <v>28</v>
       </c>
       <c r="B113" s="17">
-        <f t="shared" ref="B113:H113" si="19">COUNT(B13:B112)</f>
+        <f t="shared" ref="B113" si="19">COUNT(B13:B112)</f>
         <v>0</v>
       </c>
       <c r="C113" s="17">
@@ -12061,18 +12070,18 @@
     <row r="124" spans="1:21" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="V11:AA11"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="O11:T11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="18" orientation="portrait" r:id="rId1"/>
